--- a/scripts/productos-digitales/guia-chocolateria/build/checklist-equipamiento-y-proveedores-cacao.xlsx
+++ b/scripts/productos-digitales/guia-chocolateria/build/checklist-equipamiento-y-proveedores-cacao.xlsx
@@ -1493,7 +1493,7 @@
       </c>
       <c r="AA15" s="9" t="inlineStr">
         <is>
-          <t>El corazon del obrador y la decision 2 del bonus 2. Base de IVA NO declarada: la ficha trae el indicio «/Neto» en la linea de embalaje, que no es confirmable. La escalera completa va de esta a la Cento EX de 100 kg (`CHS-41g`), y la eleccion la decide los kg/semana que salga en la hoja de capacidad del libro 1.</t>
+          <t>El corazón del obrador y la decisión 2 del bonus 2. Base de IVA NO declarada: la ficha trae el indicio «/Neto» en la línea de embalaje, que no es confirmable. La escalera completa va de esta a la Cento EX de 100 kg (`CHS-41g`), y la elección la decide los kg/semana que salga en la hoja de capacidad del libro 1.</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="AA16" s="9" t="inlineStr">
         <is>
-          <t>La linea que nadie presupuesta: es el 12 % del precio de la maquina. La ficha la marca «Neto», que es un INDICIO de base sin IVA, no una declaracion: por eso va como «no declarada».</t>
+          <t>La línea que nadie presupuesta: es el 12 % del precio de la máquina. La ficha la marca «Neto», que es un INDICIO de base sin IVA, no una declaración: por eso va como «no declarada».</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Temperador de bano maria digital, 22 L</t>
+          <t>Temperador de baño maria digital, 22 L</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>bano maria digital 22 L</t>
+          <t>baño maria digital 22 L</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="AA19" s="9" t="inlineStr">
         <is>
-          <t>Segunda linea de templado: sin ella no se trabajan dos coberturas a la vez.</t>
+          <t>Segunda línea de templado: sin ella no se trabajan dos coberturas a la vez.</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="AA21" s="9" t="inlineStr">
         <is>
-          <t>NO esta en la dotacion de La Almendra: es la maquina del ESCENARIO B, el arranque minimo, y aparece para que el lector vea la escalera. Cubeta adicional, 165,30 euros (`CHS-41h`).</t>
+          <t>NO esta en la dotación de La Almendra: es la máquina del ESCENARIO B, el arranque mínimo, y aparece para que el lector vea la escalera. Cubeta adicional, 165,30 euros (`CHS-41h`).</t>
         </is>
       </c>
     </row>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Vitrina refrigerada especifica para chocolate</t>
+          <t>Vitrina refrigerada específica para chocolate</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Frio</t>
+          <t>Frío</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Frio</t>
+          <t>Frío</t>
         </is>
       </c>
       <c r="H23" s="15" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="AA23" s="9" t="inlineStr">
         <is>
-          <t>600x730x1380 mm. RANGO DE TRABAJO DEL EQUIPO: +14 a +17 grados C, con base SIN IVA declarada literalmente por la ficha. NO son los +2/+4 grados C de una vitrina de pasteleria, que arruina el bombon por condensacion, sugar bloom y perdida de brillo. El OBJETIVO OPERATIVO es otra cosa y lo pone el kit: 16-18 grados C y menos del 55 % de humedad. El semaforo del libro 5 solo avisa por encima de 20 grados C, y queda PROHIBIDO uno que ponga en rojo los 16-18 del propio kit. Precio de oferta (antes 3.487,00 euros): esta FECHADO el 12-09-2026 y puede caducar.</t>
+          <t>600x730x1380 mm. RANGO DE TRABAJO DEL EQUIPO: +14 a +17 °C, con base SIN IVA declarada literalmente por la ficha. NO son los +2/+4 °C de una vitrina de pastelería, que arruina el bombón por condensación, sugar bloom y perdida de brillo. El OBJETIVO OPERATIVO es otra cosa y lo pone el kit: 16-18 °C y menos del 55 % de humedad. El semáforo del libro 5 solo avisa por encima de 20 °C, y queda PROHIBIDO uno que ponga en rojo los 16-18 del propio kit. Precio de oferta (antes 3.487,00 euros): esta FECHADO el 12-09-2026 y puede caducar.</t>
         </is>
       </c>
     </row>
@@ -2436,19 +2436,19 @@
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Camara climatizada de chocolate, unos 6 m2</t>
+          <t>Cámara climatizada de chocolate, unos 6 m²</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Frio</t>
+          <t>Frío</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Frio</t>
+          <t>Frío</t>
         </is>
       </c>
       <c r="H24" s="15" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="AA24" s="9" t="inlineStr">
         <is>
-          <t>SUPUESTO declarado: ninguna fuente del research publica el precio de una camara de chocolate. Celda verde con valor por defecto. No es una nevera: trabaja a 15-18 grados C y 50-60 % de humedad, y ese control de HUMEDAD es lo que la encarece frente a una camara de pasteleria.</t>
+          <t>SUPUESTO declarado: ninguna fuente del research publica el precio de una cámara de chocolate. Celda verde con valor por defecto. No es una nevera: trabaja a 15-18 °C y 50-60 % de humedad, y ese control de HUMEDAD es lo que la encarece frente a una cámara de pastelería.</t>
         </is>
       </c>
     </row>
@@ -2551,12 +2551,12 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Frio</t>
+          <t>Frío</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Frio</t>
+          <t>Frío</t>
         </is>
       </c>
       <c r="H25" s="15" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="AA25" s="9" t="inlineStr">
         <is>
-          <t>SUPUESTO. Es la del RELLENO, a 0-4 grados C, no la del bombon acabado. Confundirlas es el error de metodo que la SPEC persigue.</t>
+          <t>SUPUESTO. Es la del RELLENO, a 0-4 °C, no la del bombón acabado. Confundirlas es el error de método que la SPEC persigue.</t>
         </is>
       </c>
     </row>
@@ -2652,7 +2652,7 @@
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Moldes de policarbonato para bomboneria (24 unidades)</t>
+          <t>Moldes de policarbonato para bombonería (24 unidades)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="AA26" s="9" t="inlineStr">
         <is>
-          <t>SE PUBLICA COMO RANGO (D23a). El unico dato medido es 24,20-42,83 euros/ud (`CHS-45a`): 24 moldes valen entre 580,80 y 1.027,92 euros. El valor por defecto (804,36) es el punto medio del rango, y es SUPUESTO. Escribir una multiplicacion con un precio unitario elegido a ojo esta prohibido. Y los moldes de policarbonato NO pagan el impuesto al plastico: no estan sujetos por el art. 73.d) de la Ley 7/2022 (`CHN-62c`), porque no se entregan junto con la mercancia.</t>
+          <t>SE PUBLICA COMO RANGO (D23a). El único dato medido es 24,20-42,83 euros/ud (`CHS-45a`): 24 moldes valen entre 580,80 y 1.027,92 euros. El valor por defecto (804,36) es el punto medio del rango, y es SUPUESTO. Escribir una multiplicación con un precio unitario elegido a ojo esta prohibido. Y los moldes de policarbonato NO pagan el impuesto al plastico: no están sujetos por el art. 73.d) de la Ley 7/2022 (`CHN-62c`), porque no se entregan junto con la mercancía.</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AA27" s="9" t="inlineStr">
         <is>
-          <t>SUPUESTO: la web del proveedor de packaging verificado devolvio HTTP 403 y no publica precio (`CHS-54`). En bomboneria la caja ES el producto en campana, y el personalizado obliga a pedidos grandes: es dinero parado en el almacen. Si lo compras fuera de Espana, mira el contador de plastico del libro 2 (`PLASTICO`).</t>
+          <t>SUPUESTO: la web del proveedor de packaging verificado devolvió HTTP 403 y no publica precio (`CHS-54`). En bombonería la caja ES el producto en campana, y el personalizado obliga a pedidos grandes: es dinero parado en el almacén. Si lo compras fuera de Espana, mira el contador de plastico del libro 2 (`PLASTICO`).</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Mobiliario de tienda, mostrador y estanteria</t>
+          <t>Mobiliario de tienda, mostrador y estantería</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>TPV, informatica y rotulo</t>
+          <t>TPV, informática y rótulo</t>
         </is>
       </c>
       <c r="H29" s="15" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="AA29" s="9" t="inlineStr">
         <is>
-          <t>SUPUESTO. La impresora de etiquetas deja de ser opcional en cuanto una sola referencia sale envasada con etiqueta (D47). Y Verifactu no es 2026, es 2027: 1-ene para sociedades y 1-jul para autonomos (`CHN-75`).</t>
+          <t>SUPUESTO. La impresora de etiquetas deja de ser opcional en cuanto una sola referencia sale envasada con etiqueta (D47). Y Verifactu no es 2026, es 2027: 1-ene para sociedades y 1-jul para autónomos (`CHN-75`).</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Climatizacion del obrador con deshumidificacion</t>
+          <t>Climatización del obrador con deshumidificación</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Climatizacion y deshumidificacion</t>
+          <t>Climatización y deshumidificación</t>
         </is>
       </c>
       <c r="H30" s="15" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="AA30" s="9" t="inlineStr">
         <is>
-          <t>SUPUESTO declarado, y es la partida que nadie presupuesta. El libro 1 NO calcula carga termica (D33): no hay un solo coeficiente con fuente ni de transmitancia, ni por m3, ni de aportes, ni de renovaciones. Lo que hace es (a) un semaforo de coherencia entre la temperatura objetivo, la exterior de agosto de TU ciudad y la potencia frigorifica que te OFREZCA EL INSTALADOR, y (b) una ficha de preguntas para el instalador. PROHIBIDO el climatizador evaporativo: anade humedad, que es justo lo contrario de lo que necesita un obrador de chocolate.</t>
+          <t>SUPUESTO declarado, y es la partida que nadie presupuesta. El libro 1 NO calcula carga térmica (D33): no hay un solo coeficiente con fuente ni de transmitancia, ni por m³, ni de aportes, ni de renovaciones. Lo que hace es (a) un semáforo de coherencia entre la temperatura objetivo, la exterior de agosto de TU ciudad y la potencia frigorífica que te OFREZCA EL INSTALADOR, y (b) una ficha de preguntas para el instalador. PROHIBIDO el climatizador evaporativo: añade humedad, que es justo lo contrario de lo que necesita un obrador de chocolate.</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="AA31" s="9" t="inlineStr">
         <is>
-          <t>Base SIN IVA declarada literalmente por la ficha. Solo entra en el escenario de taza y churros, que es OTRO negocio (D1): la Ley 12/2012 los separa sola, porque su Anexo incluye el epigrafe 644.5 de bombones y caramelos y NO contiene ningun grupo de la agrupacion 67, donde esta la chocolateria de taza (`CHN-49c`).</t>
+          <t>Base SIN IVA declarada literalmente por la ficha. Solo entra en el escenario de taza y churros, que es OTRO negocio (D1): la Ley 12/2012 los separa sola, porque su Anexo incluye el epígrafe 644.5 de bombones y caramelos y NO contiene ningún grupo de la agrupación 67, donde esta la chocolatería de taza (`CHN-49c`).</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Balanza de precision para la formulacion</t>
+          <t>Balanza de precisión para la formulación</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Precio de la maquina puesta en Espana, con transporte, aduana y puesta en marcha desglosados: los catalogos existen y estan verificados, pero los precios NO son publicos (venta a presupuesto o tienda fuera de la UE).</t>
+          <t>Precio de la máquina puesta en Espana, con transporte, aduana y puesta en marcha desglosados: los catálogos existen y están verificados, pero los precios NO son publicos (venta a presupuesto o tienda fuera de la UE).</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Potencia electrica y si necesita trifasica.</t>
+          <t>Potencia eléctrica y si necesita trifasica.</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Ruido en dB a un metro: el tostador y el winnower son los dos equipos ruidosos de un obrador que por lo demas es silencioso.</t>
+          <t>Ruido en dB a un metro: el tostador y el winnower son los dos equipos ruidosos de un obrador que por lo demás es silencioso.</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Extraccion de humos</t>
+          <t>Extracción de humos</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="C40" s="30" t="str">
-        <f>IFERROR(IF($C$6&lt;&gt;$A$46,"No es tu variante","Si hay freidora de gas, inspeccion periodica obligatoria de la instalacion receptora CADA CINCO ANOS, que en instalaciones de hasta 70 kW incluye los aparatos y comprueba la ventilacion y el volumen minimo del local "),"")</f>
+        <f>IFERROR(IF($C$6&lt;&gt;$A$46,"No es tu variante","Si hay freidora de gas, inspección periódica obligatoria de la instalación receptora CADA CINCO AÑOS, que en instalaciones de hasta 70 kW incluye los aparatos y comprueba la ventilación y el volumen mínimo del local "),"")</f>
         <v>No es tu variante</v>
       </c>
     </row>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="P7" s="9" t="inlineStr">
         <is>
-          <t>Mayor grupo del sector con presencia industrial en Espana. De aqui sale la referencia de precio del juego de datos (`CHS-28a`): Callebaut 811, bloque de 5 kg a 125,08 euros CON IVA, o sea 25,02 euros/kg.</t>
+          <t>Mayor grupo del sector con presencia industrial en Espana. De aquí sale la referencia de precio del juego de datos (`CHS-28a`): Callebaut 811, bloque de 5 kg a 125,08 euros CON IVA, o sea 25,02 euros/kg.</t>
         </is>
       </c>
     </row>
@@ -5014,7 +5014,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Asociacion Chocolate Bean to Bar Espana</t>
+          <t>Asociación Chocolate Bean to Bar Espana</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -5078,7 +5078,7 @@
       </c>
       <c r="P8" s="9" t="inlineStr">
         <is>
-          <t>La via fiable para el grano: su listado publico permite identificar a los makers y a los importadores. Se publica como «MAS DE 40 MIEMBROS», nunca con una cifra cerrada (`N-18` prohibe «45 miembros»). Ojo: las webs individuales de los proveedores de grano NO se abrieron, asi que no se publica ninguna.</t>
+          <t>La vía fiable para el grano: su listado publico permite identificar a los makers y a los importadores. Se publica como «MAS DE 40 MIEMBROS», nunca con una cifra cerrada (`N-18` prohíbe «45 miembros»). Ojo: las webs individuales de los proveedores de grano NO se abrieron, así que no se publica ninguna.</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Moldes de bomboneria y utensilios</t>
+          <t>Moldes de bombonería y utensilios</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="P10" s="9" t="inlineStr">
         <is>
-          <t>Moldes Chocolate World, Pavoni y Martellato. De aqui sale el rango de 24,20-42,83 euros/ud (`CHS-45a`) que el juego de datos publica COMO RANGO.</t>
+          <t>Moldes Chocolate World, Pavoni y Martellato. De aquí sale el rango de 24,20-42,83 euros/ud (`CHS-45a`) que el juego de datos publica COMO RANGO.</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="P11" s="9" t="inlineStr">
         <is>
-          <t>Personalizacion con logo desde pocas unidades. Su web devolvio HTTP 403 al intentar leer precios, asi que el packaging del CAPEX es SUPUESTO.</t>
+          <t>Personalización con logo desde pocas unidades. Su web devolvió HTTP 403 al intentar leer precios, así que el packaging del CAPEX es SUPUESTO.</t>
         </is>
       </c>
     </row>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="P12" s="9" t="inlineStr">
         <is>
-          <t>Dos reglas operativas verificadas del canal corporativo: plazo de entrega de 14-16 dias desde la aprobacion de la muestra virtual, y minimos de fabricacion de 10 a 25 cajas. El plazo es lo que decide si aceptas un pedido de empresa en diciembre.</t>
+          <t>Dos reglas operativas verificadas del canal corporativo: plazo de entrega de 14-16 días desde la aprobación de la muestra virtual, y mínimos de fabricación de 10 a 25 cajas. El plazo es lo que decide si aceptas un pedido de empresa en diciembre.</t>
         </is>
       </c>
     </row>
@@ -5648,14 +5648,14 @@
     <row r="36" ht="48" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Seis proveedores con URL comprobada el 12-09-2026. El research recogio muchos mas sin verificar y NO se publican. La columna «papel EUDR» va VACIA: la rellena el lector preguntando, y el numero de DDS solo se pide en la rama «operador» (D48). Directorio del grupo: hosply.pro, y su TLS se comprueba ANTES de enlazarlo desde el cap. 13 (precedente: ingredientsindex.pro tiene el certificado roto y 62 posts del blog enlazan a un aviso de seguridad).</t>
+          <t>Seis proveedores con URL comprobada el 12-09-2026. El research recogió muchos mas sin verificar y NO se publican. La columna «papel EUDR» va VACIA: la rellena el lector preguntando, y el número de DDS solo se pide en la rama «operador» (D48). Directorio del grupo: hosply.pro, y su TLS se comprueba ANTES de enlazarlo desde el cap. 13 (precedente: ingredientsindex.pro tiene el certificado roto y 62 posts del blog enlazan a un aviso de seguridad).</t>
         </is>
       </c>
     </row>
     <row r="37" ht="76" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>REDACCION OBLIGATORIA, y el paso es INFERENCIA DECLARADA, no nivel A: «si tu cobertura llega ya comercializada en la UE y amparada por una declaracion de diligencia debida, eres operador posterior (art. 2.15 ter) y el aplazamiento del art. 38.3 -que es para operadores- no te alcanza: tu fecha es el 30 de diciembre de 2026. Si tu cobertura NO esta amparada (compra anterior al EUDR, proveedor que no lo acredita), la calificacion deja de ser automatica y hay que revisarla». Estan PROHIBIDAS «siempre eres operador posterior» y «tu fecha es el 30-12-2026 pase lo que pase». Y la exclusion de los operadores posteriores del punto 15 se PARAFRASEA, no se entrecomilla: consta en la nota de `CHN-22`, no entre las 81 citas del gate de literalidad. Verificado a 12-09-2026: comprueba el estado del EUDR antes de comprar cacao.</t>
+          <t>REDACCION OBLIGATORIA, y el paso es INFERENCIA DECLARADA, no nivel A: «si tu cobertura llega ya comercializada en la UE y amparada por una declaración de diligencia debida, eres operador posterior (art. 2.15 ter) y el aplazamiento del art. 38.3 -que es para operadores- no te alcanza: tu fecha es el 30 de diciembre de 2026. Si tu cobertura NO esta amparada (compra anterior al EUDR, proveedor que no lo acredita), la calificación deja de ser automática y hay que revisarla». Están PROHIBIDAS «siempre eres operador posterior» y «tu fecha es el 30-12-2026 pase lo que pase». Y la exclusión de los operadores posteriores del punto 15 se PARAFRASEA, no se entrecomilla: consta en la nota de `CHN-22`, no entre las 81 citas del gate de literalidad. Verificado a 12-09-2026: comprueba el estado del EUDR antes de comprar cacao.</t>
         </is>
       </c>
     </row>
@@ -5899,7 +5899,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Cafeteria El Mirador</t>
+          <t>Cafetería El Mirador</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="F10" s="32" t="inlineStr">
         <is>
-          <t>Bombones de coleccion a granel y tabletas</t>
+          <t>Bombones de colección a granel y tabletas</t>
         </is>
       </c>
       <c r="G10" s="29" t="n">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="F11" s="32" t="inlineStr">
         <is>
-          <t>Bombon de cortesia de habitacion y cajas de 12</t>
+          <t>Bombón de cortesia de habitación y cajas de 12</t>
         </is>
       </c>
       <c r="G11" s="29" t="n">
@@ -6489,8 +6489,8 @@
     <row r="36" ht="76" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>CUATRO CLIENTES FICTICIOS DECLARADOS, para que la tabla del libro 9 tenga forma. Lo que NO es ficticio es la obligacion: registrar a quien suministras (art. 5.3.b) del EUDR, `CHN-24`) y conservarlo cinco anos. Escribir «basta con registrar a tus proveedores» esta PROHIBIDO (§5.1, prohibicion 3).
-Y el cuarto cliente es el que cambia tu regimen sanitario: «Tienda gourmet La Despensa» es un MINORISTA DE DISTINTA TITULARIDAD, asi que activa el art. 3 del RD 1021/2022 (`CHN-41`). Basta con que UNO de tus clientes este inscrito en el RGSEAA para romper el requisito de «restringido», y los tres requisitos son ACUMULATIVOS.</t>
+          <t>CUATRO CLIENTES FICTICIOS DECLARADOS, para que la tabla del libro 9 tenga forma. Lo que NO es ficticio es la obligación: registrar a quien suministras (art. 5.3.b) del EUDR, `CHN-24`) y conservarlo cinco años. Escribir «basta con registrar a tus proveedores» esta PROHIBIDO (§5.1, prohibición 3).
+Y el cuarto cliente es el que cambia tu régimen sanitario: «Tienda gourmet La Despensa» es un MINORISTA DE DISTINTA TITULARIDAD, así que activa el art. 3 del RD 1021/2022 (`CHN-41`). Basta con que UNO de tus clientes este inscrito en el RGSEAA para romper el requisito de «restringido», y los tres requisitos son ACUMULATIVOS.</t>
         </is>
       </c>
     </row>

--- a/scripts/productos-digitales/guia-chocolateria/build/checklist-equipamiento-y-proveedores-cacao.xlsx
+++ b/scripts/productos-digitales/guia-chocolateria/build/checklist-equipamiento-y-proveedores-cacao.xlsx
@@ -829,7 +829,7 @@
     <row r="8" ht="64" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>3. Hoja «Proveedores y EUDR»: los seis proveedores con URL comprobada, y el árbol que decide qué papeles le tocan a cada uno. Pregúntale a cada proveedor si es operador, operador posterior o comerciante: el número de referencia de su declaración de diligencia debida SÓLO se le pide al primero. Y en las dos últimas columnas, los boletines de cadmio y de HAP.</t>
+          <t>3. Hoja «Proveedores y EUDR»: los seis proveedores publicados —cinco con URL comprobada el 12-09-2026 y uno, SelfPackaging, pendiente—, y el árbol que decide qué papeles le tocan a cada uno. Pregúntale a cada proveedor si es operador, operador posterior o comerciante: el número de referencia de su declaración de diligencia debida SÓLO se le pide al primero. Y en las dos últimas columnas, los boletines de cadmio y de HAP.</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
     <row r="17" ht="76" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>NO SE PUBLICAN LOS PROVEEDORES SIN VERIFICAR. El research recogió muchos más; aquí entran los seis con URL comprobada el 12 de septiembre de 2026. Un directorio con un enlace roto vale menos que uno corto.</t>
+          <t>NO SE PUBLICAN LOS PROVEEDORES SIN VERIFICAR. El research recogió muchos más; aquí entran los seis publicados: cinco con URL comprobada el 12 de septiembre de 2026 y uno (SelfPackaging) pendiente, con su web devolviendo un HTTP 403 ese día. Un directorio con un enlace roto vale menos que uno corto.</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AA73"/>
+  <dimension ref="A1:AB73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1113,6 +1113,7 @@
     <col width="28" customWidth="1" min="25" max="25"/>
     <col width="22" customWidth="1" min="26" max="26"/>
     <col width="78" customWidth="1" min="27" max="27"/>
+    <col width="36" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1380,6 +1381,11 @@
           <t>Nota</t>
         </is>
       </c>
+      <c r="AB14" s="7" t="inlineStr">
+        <is>
+          <t>Precio tal como se publica</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" s="13" t="inlineStr">
@@ -1496,6 +1502,11 @@
           <t>El corazón del obrador y la decisión 2 del bonus 2. Base de IVA NO declarada: la ficha trae el indicio «/Neto» en la línea de embalaje, que no es confirmable. La escalera completa va de esta a la Cento EX de 100 kg (`CHS-41g`), y la elección la decide los kg/semana que salga en la hoja de capacidad del libro 1.</t>
         </is>
       </c>
+      <c r="AB15" s="9" t="inlineStr">
+        <is>
+          <t>8.500 €</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="40" customHeight="1">
       <c r="A16" s="13" t="inlineStr">
@@ -1612,6 +1623,11 @@
           <t>La línea que nadie presupuesta: es el 12 % del precio de la máquina. La ficha la marca «Neto», que es un INDICIO de base sin IVA, no una declaración: por eso va como «no declarada».</t>
         </is>
       </c>
+      <c r="AB16" s="9" t="inlineStr">
+        <is>
+          <t>1.045 €</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" s="13" t="inlineStr">
@@ -1728,6 +1744,11 @@
           <t>Base de IVA NO declarada por la ficha del distribuidor.</t>
         </is>
       </c>
+      <c r="AB17" s="9" t="inlineStr">
+        <is>
+          <t>6.800 €</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" s="13" t="inlineStr">
@@ -1844,6 +1865,11 @@
           <t>Base de IVA NO declarada por la ficha del distribuidor.</t>
         </is>
       </c>
+      <c r="AB18" s="9" t="inlineStr">
+        <is>
+          <t>1.495 €</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" s="13" t="inlineStr">
@@ -1856,7 +1882,7 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Temperador de baño maria digital, 22 L</t>
+          <t>Temperador de baño maría digital, 22 L</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1866,7 +1892,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>baño maria digital 22 L</t>
+          <t>baño maría digital 22 L</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1960,6 +1986,11 @@
           <t>Segunda línea de templado: sin ella no se trabajan dos coberturas a la vez.</t>
         </is>
       </c>
+      <c r="AB19" s="9" t="inlineStr">
+        <is>
+          <t>2.650 €</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="40" customHeight="1">
       <c r="A20" s="13" t="inlineStr">
@@ -2076,6 +2107,11 @@
           <t>ES UN «DESDE», NO UN PRECIO (D23b): la ficha publica «desde 570,00 euros» y eso es un SUELO comercial, no el precio de la unidad que vas a comprar. Se presupuesta. Publicarlo como precio cerrado esta prohibido, y el techo del escenario B solo puede subir por su culpa.</t>
         </is>
       </c>
+      <c r="AB20" s="9" t="inlineStr">
+        <is>
+          <t>desde 570 € (suelo, presupuestar)</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="40" customHeight="1">
       <c r="A21" s="13" t="inlineStr">
@@ -2192,6 +2228,11 @@
           <t>NO esta en la dotación de La Almendra: es la máquina del ESCENARIO B, el arranque mínimo, y aparece para que el lector vea la escalera. Cubeta adicional, 165,30 euros (`CHS-41h`).</t>
         </is>
       </c>
+      <c r="AB21" s="9" t="inlineStr">
+        <is>
+          <t>1.960 €</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="40" customHeight="1">
       <c r="A22" s="13" t="inlineStr">
@@ -2308,6 +2349,11 @@
           <t>Accesorio del escenario B.</t>
         </is>
       </c>
+      <c r="AB22" s="9" t="inlineStr">
+        <is>
+          <t>165,30 €</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" s="13" t="inlineStr">
@@ -2424,6 +2470,11 @@
           <t>600x730x1380 mm. RANGO DE TRABAJO DEL EQUIPO: +14 a +17 °C, con base SIN IVA declarada literalmente por la ficha. NO son los +2/+4 °C de una vitrina de pastelería, que arruina el bombón por condensación, sugar bloom y perdida de brillo. El OBJETIVO OPERATIVO es otra cosa y lo pone el kit: 16-18 °C y menos del 55 % de humedad. El semáforo del libro 5 solo avisa por encima de 20 °C, y queda PROHIBIDO uno que ponga en rojo los 16-18 del propio kit. Precio de oferta (antes 3.487,00 euros): esta FECHADO el 12-09-2026 y puede caducar.</t>
         </is>
       </c>
+      <c r="AB23" s="9" t="inlineStr">
+        <is>
+          <t>2.684,99 €</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="40" customHeight="1">
       <c r="A24" s="13" t="inlineStr">
@@ -2532,6 +2583,11 @@
           <t>SUPUESTO declarado: ninguna fuente del research publica el precio de una cámara de chocolate. Celda verde con valor por defecto. No es una nevera: trabaja a 15-18 °C y 50-60 % de humedad, y ese control de HUMEDAD es lo que la encarece frente a una cámara de pastelería.</t>
         </is>
       </c>
+      <c r="AB24" s="9" t="inlineStr">
+        <is>
+          <t>6.400 €</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="40" customHeight="1">
       <c r="A25" s="13" t="inlineStr">
@@ -2640,6 +2696,11 @@
           <t>SUPUESTO. Es la del RELLENO, a 0-4 °C, no la del bombón acabado. Confundirlas es el error de método que la SPEC persigue.</t>
         </is>
       </c>
+      <c r="AB25" s="9" t="inlineStr">
+        <is>
+          <t>1.450 €</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="40" customHeight="1">
       <c r="A26" s="13" t="inlineStr">
@@ -2756,6 +2817,11 @@
           <t>SE PUBLICA COMO RANGO (D23a). El único dato medido es 24,20-42,83 euros/ud (`CHS-45a`): 24 moldes valen entre 580,80 y 1.027,92 euros. El valor por defecto (804,36) es el punto medio del rango, y es SUPUESTO. Escribir una multiplicación con un precio unitario elegido a ojo esta prohibido. Y los moldes de policarbonato NO pagan el impuesto al plastico: no están sujetos por el art. 73.d) de la Ley 7/2022 (`CHN-62c`), porque no se entregan junto con la mercancía.</t>
         </is>
       </c>
+      <c r="AB26" s="9" t="inlineStr">
+        <is>
+          <t>580,80 - 1.027,92 € (RANGO, no es un precio)</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="40" customHeight="1">
       <c r="A27" s="13" t="inlineStr">
@@ -2861,7 +2927,12 @@
       </c>
       <c r="AA27" s="9" t="inlineStr">
         <is>
-          <t>SUPUESTO: la web del proveedor de packaging verificado devolvió HTTP 403 y no publica precio (`CHS-54`). En bombonería la caja ES el producto en campana, y el personalizado obliga a pedidos grandes: es dinero parado en el almacén. Si lo compras fuera de Espana, mira el contador de plastico del libro 2 (`PLASTICO`).</t>
+          <t>SUPUESTO: la web del proveedor de packaging verificado devolvió HTTP 403 y no publica precio (`CHS-54`). En bombonería la caja ES el producto en campana, y el personalizado obliga a pedidos grandes: es dinero parado en el almacén. Si lo compras fuera de España, mira el contador de plastico del libro 2 (`PLASTICO`).</t>
+        </is>
+      </c>
+      <c r="AB27" s="9" t="inlineStr">
+        <is>
+          <t>2.200 €</t>
         </is>
       </c>
     </row>
@@ -2972,6 +3043,11 @@
           <t>SUPUESTO declarado. Celda verde con valor por defecto.</t>
         </is>
       </c>
+      <c r="AB28" s="9" t="inlineStr">
+        <is>
+          <t>6.900 €</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="40" customHeight="1">
       <c r="A29" s="13" t="inlineStr">
@@ -2984,7 +3060,7 @@
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>TPV, ordenador, impresora de etiquetas y rotulo</t>
+          <t>TPV, ordenador, impresora de etiquetas y rótulo</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -3080,6 +3156,11 @@
           <t>SUPUESTO. La impresora de etiquetas deja de ser opcional en cuanto una sola referencia sale envasada con etiqueta (D47). Y Verifactu no es 2026, es 2027: 1-ene para sociedades y 1-jul para autónomos (`CHN-75`).</t>
         </is>
       </c>
+      <c r="AB29" s="9" t="inlineStr">
+        <is>
+          <t>3.200 €</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="40" customHeight="1">
       <c r="A30" s="13" t="inlineStr">
@@ -3188,6 +3269,11 @@
           <t>SUPUESTO declarado, y es la partida que nadie presupuesta. El libro 1 NO calcula carga térmica (D33): no hay un solo coeficiente con fuente ni de transmitancia, ni por m³, ni de aportes, ni de renovaciones. Lo que hace es (a) un semáforo de coherencia entre la temperatura objetivo, la exterior de agosto de TU ciudad y la potencia frigorífica que te OFREZCA EL INSTALADOR, y (b) una ficha de preguntas para el instalador. PROHIBIDO el climatizador evaporativo: añade humedad, que es justo lo contrario de lo que necesita un obrador de chocolate.</t>
         </is>
       </c>
+      <c r="AB30" s="9" t="inlineStr">
+        <is>
+          <t>7.600 €</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="40" customHeight="1">
       <c r="A31" s="13" t="inlineStr">
@@ -3302,6 +3388,11 @@
       <c r="AA31" s="9" t="inlineStr">
         <is>
           <t>Base SIN IVA declarada literalmente por la ficha. Solo entra en el escenario de taza y churros, que es OTRO negocio (D1): la Ley 12/2012 los separa sola, porque su Anexo incluye el epígrafe 644.5 de bombones y caramelos y NO contiene ningún grupo de la agrupación 67, donde esta la chocolatería de taza (`CHN-49c`).</t>
+        </is>
+      </c>
+      <c r="AB31" s="9" t="inlineStr">
+        <is>
+          <t>527 €</t>
         </is>
       </c>
     </row>
@@ -3781,9 +3872,11 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="58">
     <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A68:AB68"/>
     <mergeCell ref="K47:AA47"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="K49:AA49"/>
+    <mergeCell ref="A69:AB69"/>
     <mergeCell ref="K34:AA34"/>
     <mergeCell ref="K46:AA46"/>
     <mergeCell ref="A53:H53"/>
@@ -3791,7 +3884,6 @@
     <mergeCell ref="A40:H40"/>
     <mergeCell ref="K57:AA57"/>
     <mergeCell ref="K53:AA53"/>
-    <mergeCell ref="A3:AA3"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A73:F73"/>
     <mergeCell ref="A47:H47"/>
@@ -3799,17 +3891,17 @@
     <mergeCell ref="K48:AA48"/>
     <mergeCell ref="A37:H37"/>
     <mergeCell ref="K41:AA41"/>
-    <mergeCell ref="A68:AA68"/>
-    <mergeCell ref="A70:AA70"/>
     <mergeCell ref="K42:AA42"/>
     <mergeCell ref="K54:AA54"/>
     <mergeCell ref="K37:AA37"/>
     <mergeCell ref="A55:H55"/>
     <mergeCell ref="K56:AA56"/>
     <mergeCell ref="D6:AA6"/>
+    <mergeCell ref="A70:AB70"/>
     <mergeCell ref="A34:H34"/>
     <mergeCell ref="A46:H46"/>
     <mergeCell ref="A48:H48"/>
+    <mergeCell ref="A3:AB3"/>
     <mergeCell ref="K50:AA50"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A42:H42"/>
@@ -3823,7 +3915,6 @@
     <mergeCell ref="A57:H57"/>
     <mergeCell ref="K40:AA40"/>
     <mergeCell ref="D10:AA10"/>
-    <mergeCell ref="A69:AA69"/>
     <mergeCell ref="K36:AA36"/>
     <mergeCell ref="D8:AA8"/>
     <mergeCell ref="A11:B11"/>
@@ -4328,7 +4419,7 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Precio de la máquina puesta en Espana, con transporte, aduana y puesta en marcha desglosados: los catálogos existen y están verificados, pero los precios NO son publicos (venta a presupuesto o tienda fuera de la UE).</t>
+          <t>Precio de la máquina puesta en España, con transporte, aduana y puesta en marcha desglosados: los catálogos existen y están verificados, pero los precios NO son publicos (venta a presupuesto o tienda fuera de la UE).</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
@@ -4352,7 +4443,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Plazo de entrega real y quien hace el mantenimiento en Espana.</t>
+          <t>Plazo de entrega real y quien hace el mantenimiento en España.</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
@@ -4840,7 +4931,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Los seis con URL comprobada el 12-09-2026. La columna que decide es la G: el número de referencia de la declaración de diligencia debida SÓLO se le pide a un operador. Pedírselo a un comerciante es pedirle algo que no tiene.</t>
+          <t>Cinco con URL comprobada el 12-09-2026 y uno (SelfPackaging) pendiente: HTTP 403 ese día. La columna que decide es la G: el número de referencia de la declaración de diligencia debida SÓLO se le pide a un operador. Pedírselo a un comerciante es pedirle algo que no tiene.</t>
         </is>
       </c>
     </row>
@@ -4848,7 +4939,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Los seis proveedores verificados</t>
+          <t>Los seis proveedores publicados</t>
         </is>
       </c>
     </row>
@@ -4940,7 +5031,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Callebaut / Barry Callebaut Iberica</t>
+          <t>Callebaut / Barry Callebaut Ibérica</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -5004,7 +5095,7 @@
       </c>
       <c r="P7" s="9" t="inlineStr">
         <is>
-          <t>Mayor grupo del sector con presencia industrial en Espana. De aquí sale la referencia de precio del juego de datos (`CHS-28a`): Callebaut 811, bloque de 5 kg a 125,08 euros CON IVA, o sea 25,02 euros/kg.</t>
+          <t>Mayor grupo del sector con presencia industrial en España. De aquí sale la referencia de precio del juego de datos (`CHS-28a`): Callebaut 811, bloque de 5 kg a 125,08 euros CON IVA, o sea 25,02 euros/kg.</t>
         </is>
       </c>
     </row>
@@ -5014,7 +5105,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Asociación Chocolate Bean to Bar Espana</t>
+          <t>Asociación Chocolate Bean to Bar España</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -5246,7 +5337,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://selfpackaging.es/90-cajas-para-bombones</t>
+          <t>https://selfpackaging.es/90-cajas-para-bombones (web no accesible el 12-09-2026, HTTP 403: pendiente de comprobar)</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -5398,7 +5489,7 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>Seis verificados con URL el 12-09-2026. Los que el research recogió sin verificar no entran.</t>
+          <t>Cinco con URL comprobada el 12-09-2026 y uno (SelfPackaging) pendiente, marcado en su fila. Los que el research recogió sin verificar no entran.</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6151,7 @@
       </c>
       <c r="F13" s="32" t="inlineStr">
         <is>
-          <t>Tabletas de origen y almendras banadas</t>
+          <t>Tabletas de origen y almendras bañadas</t>
         </is>
       </c>
       <c r="G13" s="29" t="n">
@@ -6353,7 +6444,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>BASTA UNO para romper el requisito de «restringido» del art. 3, y los tres requisitos son acumulativos. Es la casilla más cara de esta hoja.</t>
+          <t>BASTA UNO para romper el requisito de «restringido» del art. 3, y los tres requisitos son acumulativos. Es la casilla más cara de esta hoja. Los «No lo sé» NO se cuentan aquí: mientras queden, este 0 no significa que ninguno esté inscrito.</t>
         </is>
       </c>
     </row>
